--- a/data/trans_orig/IP22_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>39708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34427</t>
+          <t>34414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43703</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36630</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47716</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74522</t>
+          <t>73077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>88524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27387</t>
+          <t>26695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>34154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37757</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74175</t>
+          <t>74867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87392</t>
+          <t>87589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74099</t>
+          <t>74603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>89015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153064</t>
+          <t>153495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172562</t>
+          <t>172592</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>40165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46295</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57623</t>
+          <t>57525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47709</t>
+          <t>47539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>58931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97990</t>
+          <t>97759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114579</t>
+          <t>114259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25718</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>42777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>52893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64146</t>
+          <t>63718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>55482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66959</t>
+          <t>67682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111551</t>
+          <t>111195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128254</t>
+          <t>128624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>31849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>34514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69046</t>
+          <t>69030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79335</t>
+          <t>78800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>35538</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37564</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48160</t>
+          <t>48218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>39443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>49831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>80249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96016</t>
+          <t>95424</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37552</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>40366</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>50372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72320</t>
+          <t>73340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91070</t>
+          <t>90808</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106732</t>
+          <t>106262</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95815</t>
+          <t>95289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111612</t>
+          <t>111456</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>191957</t>
+          <t>190937</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>215013</t>
+          <t>213905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>27640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35154</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37603</t>
+          <t>37010</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57143</t>
+          <t>57146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129922</t>
+          <t>130264</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143678</t>
+          <t>144406</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128904</t>
+          <t>129333</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143914</t>
+          <t>143932</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>264819</t>
+          <t>264816</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>284359</t>
+          <t>284952</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114820</t>
+          <t>114811</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>148284</t>
+          <t>148370</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>139843</t>
+          <t>140014</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>175288</t>
+          <t>175099</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>264539</t>
+          <t>264161</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>311881</t>
+          <t>315664</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>532737</t>
+          <t>532651</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>566210</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>547412</t>
+          <t>547601</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>582857</t>
+          <t>582686</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1091840</t>
+          <t>1088057</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1139182</t>
+          <t>1139560</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12562</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23528</t>
+          <t>23426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>35643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36442</t>
+          <t>37825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54329</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33899</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>45150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27372</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40957</t>
+          <t>40879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66162</t>
+          <t>64934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84049</t>
+          <t>82666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>68,61%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>26108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>41639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>31791</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47505</t>
+          <t>49242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62064</t>
+          <t>61599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84161</t>
+          <t>84485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64144</t>
+          <t>62429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78864</t>
+          <t>77960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63654</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79203</t>
+          <t>79368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131066</t>
+          <t>130742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153163</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>28157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17280</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>34690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>53007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40608</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41373</t>
+          <t>41679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53974</t>
+          <t>54714</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86043</t>
+          <t>86425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104644</t>
+          <t>104742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>26418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32060</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35135</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53639</t>
+          <t>53924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64603</t>
+          <t>64098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64777</t>
+          <t>64852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106356</t>
+          <t>106071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124860</t>
+          <t>124510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>22068</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>22560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53656</t>
+          <t>54280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68431</t>
+          <t>68585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11179</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>22318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27945</t>
+          <t>28228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28894</t>
+          <t>29721</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47134</t>
+          <t>46498</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33110</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44555</t>
+          <t>44806</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>44231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68354</t>
+          <t>68990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86594</t>
+          <t>85767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40586</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>34998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52152</t>
+          <t>53325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62536</t>
+          <t>62409</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88155</t>
+          <t>86343</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98132</t>
+          <t>97772</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>115161</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>92918</t>
+          <t>91745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111563</t>
+          <t>110072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195633</t>
+          <t>197445</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>221252</t>
+          <t>221379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35230</t>
+          <t>35300</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146385</t>
+          <t>146016</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>157407</t>
+          <t>156931</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149507</t>
+          <t>149870</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161532</t>
+          <t>161545</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>300793</t>
+          <t>300723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>316521</t>
+          <t>316135</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>149607</t>
+          <t>148063</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>187162</t>
+          <t>187006</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187350</t>
+          <t>186934</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>228833</t>
+          <t>227835</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>346823</t>
+          <t>348333</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>404113</t>
+          <t>403716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>523584</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562683</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>521519</t>
+          <t>522517</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>563002</t>
+          <t>563418</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1056984</t>
+          <t>1057381</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1114274</t>
+          <t>1112764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>27473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14942</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>34265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51920</t>
+          <t>51592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30085</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41737</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49520</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69913</t>
+          <t>70241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87099</t>
+          <t>87568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>20661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36010</t>
+          <t>36523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48225</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68401</t>
+          <t>68609</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67878</t>
+          <t>67928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82519</t>
+          <t>81459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74273</t>
+          <t>73760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88908</t>
+          <t>89622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145829</t>
+          <t>145621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166005</t>
+          <t>166457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>56107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63956</t>
+          <t>63971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62549</t>
+          <t>63010</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69166</t>
+          <t>69188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122224</t>
+          <t>121180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131711</t>
+          <t>131492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>20935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34529</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37721</t>
+          <t>38331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57630</t>
+          <t>57048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50598</t>
+          <t>50999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62265</t>
+          <t>63022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>44137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99697</t>
+          <t>100279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119606</t>
+          <t>118996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>34507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41368</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78727</t>
+          <t>79564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86795</t>
+          <t>87128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>46785</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43465</t>
+          <t>43600</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52655</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82950</t>
+          <t>82457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97032</t>
+          <t>97339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115291</t>
+          <t>115441</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127427</t>
+          <t>127268</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>126898</t>
+          <t>127164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137448</t>
+          <t>136993</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246486</t>
+          <t>247321</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261965</t>
+          <t>262350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23051</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>29948</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48629</t>
+          <t>48096</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>141125</t>
+          <t>141307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152993</t>
+          <t>153226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140875</t>
+          <t>140901</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155002</t>
+          <t>155099</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>286396</t>
+          <t>286929</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>304570</t>
+          <t>305232</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>109625</t>
+          <t>108595</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>143203</t>
+          <t>140126</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>108277</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142659</t>
+          <t>141691</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>224244</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>273282</t>
+          <t>271598</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>564245</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>594746</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>601367</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>635749</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1175115</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1220500</t>
+          <t>1224153</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37694</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28068</t>
+          <t>28664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35165</t>
+          <t>35479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60776</t>
+          <t>60624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56019</t>
+          <t>55789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>50702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>65474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91872</t>
+          <t>92024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117483</t>
+          <t>117169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42930</t>
+          <t>43312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100907</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118330</t>
+          <t>120015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103446</t>
+          <t>104355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118115</t>
+          <t>118017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211505</t>
+          <t>211123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233662</t>
+          <t>233039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18248</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39297</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49272</t>
+          <t>49045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62192</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96237</t>
+          <t>95298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109715</t>
+          <t>109211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38958</t>
+          <t>37146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>51872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62738</t>
+          <t>63268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>54063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70999</t>
+          <t>70917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109320</t>
+          <t>111132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130722</t>
+          <t>131804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>30184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34053</t>
+          <t>34066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34624</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39694</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>66831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73129</t>
+          <t>73191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35832</t>
+          <t>35972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>42899</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41662</t>
+          <t>41840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51090</t>
+          <t>50846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80917</t>
+          <t>80901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92092</t>
+          <t>92590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50542</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51150</t>
+          <t>52326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79148</t>
+          <t>78888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88897</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106565</t>
+          <t>106772</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105470</t>
+          <t>104489</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>201372</t>
+          <t>201632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>229370</t>
+          <t>228194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123974</t>
+          <t>122855</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130007</t>
+          <t>129688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>143058</t>
+          <t>143528</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152965</t>
+          <t>153007</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>270921</t>
+          <t>271212</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>281751</t>
+          <t>282107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>123880</t>
+          <t>124638</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>196171</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>251523</t>
+          <t>251730</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>540737</t>
+          <t>539979</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>580162</t>
+          <t>580609</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>626659</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>662328</t>
+          <t>662355</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1175066</t>
+          <t>1174859</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1230418</t>
+          <t>1232167</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
